--- a/output/pdf_financials_xlsx/SLA.xlsx
+++ b/output/pdf_financials_xlsx/SLA.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SLA.xlsx
+++ b/output/pdf_financials_xlsx/SLA.xlsx
@@ -1277,8 +1277,10 @@
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1296,8 +1298,10 @@
       <c r="D35" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>0.145</v>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1315,8 +1319,10 @@
       <c r="D36" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>0.145</v>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1334,8 +1340,10 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>0</v>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1353,8 +1361,10 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>0</v>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1372,8 +1382,10 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>0</v>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1391,8 +1403,10 @@
       <c r="D40" s="3" t="n">
         <v>0.267928</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>0.014605</v>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1410,8 +1424,10 @@
       <c r="D41" s="3" t="n">
         <v>0.267928</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>0.014605</v>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1429,8 +1445,10 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>0</v>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1448,8 +1466,10 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>0</v>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1467,8 +1487,10 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="3" t="n">
-        <v>0</v>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1486,8 +1508,10 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>0</v>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1505,8 +1529,10 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1524,8 +1550,10 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="3" t="n">
-        <v>0</v>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1543,8 +1571,10 @@
       <c r="D48" s="3" t="n">
         <v>0.388687</v>
       </c>
-      <c r="E48" s="3" t="n">
-        <v>0.333132</v>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1562,8 +1592,10 @@
       <c r="D49" s="3" t="n">
         <v>0.926615</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>0.492737</v>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1581,8 +1613,10 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>0</v>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1600,8 +1634,10 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="3" t="n">
-        <v>0</v>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1619,8 +1655,10 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="n">
-        <v>0</v>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1638,8 +1676,10 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="3" t="n">
-        <v>0</v>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1657,8 +1697,10 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="3" t="n">
-        <v>0</v>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1703,8 +1745,10 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1722,8 +1766,10 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="3" t="n">
-        <v>0</v>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1741,8 +1787,10 @@
       <c r="D58" s="3" t="n">
         <v>2.991209</v>
       </c>
-      <c r="E58" s="3" t="n">
-        <v>3.039766</v>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1760,8 +1808,10 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>0</v>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1779,8 +1829,10 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1798,8 +1850,10 @@
       <c r="D61" s="3" t="n">
         <v>8.73808</v>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>8.082017</v>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1817,8 +1871,10 @@
       <c r="D62" s="3" t="n">
         <v>11.729289</v>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>11.121783</v>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1836,8 +1892,10 @@
       <c r="D63" s="3" t="n">
         <v>12.655904</v>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>11.61452</v>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1855,8 +1913,10 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>0</v>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1874,8 +1934,10 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1893,8 +1955,10 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="3" t="n">
-        <v>0</v>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1912,8 +1976,10 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="3" t="n">
-        <v>0</v>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1931,8 +1997,10 @@
       <c r="D68" s="3" t="n">
         <v>0.30831</v>
       </c>
-      <c r="E68" s="3" t="n">
-        <v>0.372413</v>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1950,8 +2018,10 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1969,8 +2039,10 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="3" t="n">
-        <v>0</v>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1988,8 +2060,10 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>0</v>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2007,8 +2081,10 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="3" t="n">
-        <v>0</v>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2026,8 +2102,10 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>0</v>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2045,8 +2123,10 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>0</v>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -2064,8 +2144,10 @@
       <c r="D75" s="3" t="n">
         <v>1.279355</v>
       </c>
-      <c r="E75" s="3" t="n">
-        <v>1.456613</v>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2083,8 +2165,10 @@
       <c r="D76" s="3" t="n">
         <v>1.587665</v>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>1.829026</v>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2102,8 +2186,10 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="3" t="n">
-        <v>0</v>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2121,8 +2207,10 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="3" t="n">
-        <v>0</v>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2140,8 +2228,10 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>0</v>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2186,8 +2276,10 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="3" t="n">
-        <v>0</v>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2205,8 +2297,10 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="3" t="n">
-        <v>0</v>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2224,8 +2318,10 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2243,8 +2339,10 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>0</v>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -2262,8 +2360,10 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2281,8 +2381,10 @@
       <c r="D86" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>0</v>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2300,8 +2402,10 @@
       <c r="D87" s="3" t="n">
         <v>1.587665</v>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>1.829026</v>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2319,8 +2423,10 @@
       <c r="D88" s="3" t="n">
         <v>19.239628</v>
       </c>
-      <c r="E88" s="3" t="n">
-        <v>19.239628</v>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2338,8 +2444,10 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="3" t="n">
-        <v>0</v>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2357,8 +2465,10 @@
       <c r="D90" s="3" t="n">
         <v>-13.984437</v>
       </c>
-      <c r="E90" s="3" t="n">
-        <v>-15.267182</v>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2376,8 +2486,10 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="n">
-        <v>0</v>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2395,8 +2507,10 @@
       <c r="D92" s="3" t="n">
         <v>4.702907</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>4.921767</v>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -2414,8 +2528,10 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>0</v>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2433,8 +2549,10 @@
       <c r="D94" s="3" t="n">
         <v>11.068239</v>
       </c>
-      <c r="E94" s="3" t="n">
-        <v>9.785494</v>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2452,8 +2570,10 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="3" t="n">
-        <v>0</v>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2471,8 +2591,10 @@
       <c r="D96" s="3" t="n">
         <v>11.068239</v>
       </c>
-      <c r="E96" s="3" t="n">
-        <v>9.785494</v>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2490,8 +2612,10 @@
       <c r="D97" s="3" t="n">
         <v>0.8745514346505789</v>
       </c>
-      <c r="E97" s="3" t="n">
-        <v>0.8425224632615037</v>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -3227,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3308,8 +3432,10 @@
       <c r="G2" s="5" t="n">
         <v>0.109165</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>0.08821900000000001</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3344,8 +3470,10 @@
       <c r="G3" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>0.145</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3378,8 +3506,10 @@
       <c r="G4" s="5" t="n">
         <v>0.267928</v>
       </c>
-      <c r="H4" s="5" t="n">
-        <v>0.014605</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3446,8 +3576,10 @@
       <c r="G6" s="5" t="n">
         <v>0.004569</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0.004827</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3476,8 +3608,10 @@
       <c r="G7" s="5" t="n">
         <v>0.240086</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>0.240086</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3510,8 +3644,10 @@
       <c r="G8" s="5" t="n">
         <v>0.926615</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0.492737</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3540,8 +3676,10 @@
       <c r="G9" s="5" t="n">
         <v>8.738079000000001</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>8.521532000000001</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3574,8 +3712,10 @@
       <c r="G10" s="5" t="n">
         <v>2.991209</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <v>2.600251</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3591,25 +3731,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Total non-current assets</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TotalNonCurrentAssets</t>
-        </is>
-      </c>
+          <t>Balance of purchase price receivable 5 a)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" s="5" t="n">
-        <v>10.077679</v>
+        <v>0.375838</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>10.434374</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>11.729289</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>11.121783</v>
+        <v>0.081263</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3625,25 +3765,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Total non-current assets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>TotalNonCurrentAssets</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>11.665532</v>
+        <v>10.077679</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>13.408247</v>
+        <v>10.434374</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>12.655904</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>11.61452</v>
+        <v>11.729289</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -3654,30 +3796,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trade accounts payable and accrued liabilities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.404279</v>
+        <v>11.665532</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.422686</v>
+        <v>13.408247</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.30831</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0.372413</v>
+        <v>12.655904</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3693,21 +3837,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grants refundable 8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Trade accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
-        <v>0.33732</v>
+        <v>0.404279</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.33732</v>
+        <v>0.422686</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.33732</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0.33732</v>
+        <v>0.30831</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -3723,21 +3873,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Current portion of convertible debentures 7</t>
+          <t>Grants refundable 8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>0.231037</v>
+        <v>0.33732</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.209689</v>
+        <v>0.33732</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.942036</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1.119293</v>
+        <v>0.33732</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3753,25 +3905,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total current liabilities</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Current portion of convertible debentures 7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" s="5" t="n">
-        <v>0.985109</v>
+        <v>0.231037</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.969695</v>
+        <v>0.209689</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.587665</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>1.829026</v>
+        <v>0.942036</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3787,29 +3937,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Total current liabilities</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.985109</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.969695</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>1.587665</v>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>1.829026</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -3820,30 +3968,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share capital 9</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
+          <t>Convertible debentures 7</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" s="5" t="n">
-        <v>17.640824</v>
+        <v>0.781778</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>19.273885</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>19.239628</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>19.239628</v>
+        <v>0.784172</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -3854,26 +4002,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Warrants 9</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Total non-current liabilities</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
-        <v>0.924554</v>
+        <v>0.781778</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.5972730000000001</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.422795</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.76639</v>
+        <v>0.784172</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -3884,26 +4040,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Share options 10</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
-        <v>0.435175</v>
+        <v>1.766887</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.144092</v>
+        <v>1.753867</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.124892</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0.124892</v>
+        <v>1.587665</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3919,22 +4081,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Equity component of the convertible debentures 4.13</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital 9</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>17.640824</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>19.273885</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.562455</v>
+        <v>19.239628</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3955,25 +4117,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Warrants 9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
-        <v>3.128626</v>
+        <v>0.924554</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>4.47497</v>
+        <v>0.5972730000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>4.702907</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>4.921767</v>
+        <v>0.422795</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3989,25 +4149,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
+          <t>Share options 10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>-12.792989</v>
+        <v>0.435175</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-13.398296</v>
+        <v>0.144092</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-13.984437</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>-15.267182</v>
+        <v>0.124892</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -4023,25 +4181,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>9.898645</v>
+          <t>Equity component of the convertible debentures</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>11.65438</v>
+        <v>0.562455</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>11.068239</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>9.785494</v>
+        <v>0.562455</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -4057,25 +4215,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Total liabilities and equity</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>11.665532</v>
+        <v>3.128626</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.408247</v>
+        <v>4.47497</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>12.655904</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>11.61452</v>
+        <v>4.702907</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -4091,21 +4251,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>These consolidated financial statements were approved and authorized for issue by the Board of Directors on November</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.002023</v>
+        <v>-12.792989</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.002024</v>
+        <v>-13.398296</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1.8e-05</v>
+        <v>-13.984437</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4116,26 +4282,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>0.115203</v>
+        <v>9.898645</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.167383</v>
+        <v>11.65438</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.130834</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>0.071062</v>
+        <v>11.068239</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -4146,26 +4318,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Management and consulting fees</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.512956</v>
+        <v>11.665532</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.262</v>
+        <v>13.408247</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.249862</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.250687</v>
+        <v>12.655904</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4176,26 +4354,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Registration, listing fees and shareholders information</t>
+          <t>These consolidated financial statements were approved and authorized for issue by the Board of Directors on November</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.05251</v>
+        <v>0.002023</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.034201</v>
+        <v>0.002024</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.033244</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>0.026887</v>
+        <v>2.5e-05</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -4211,21 +4391,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Insurance and office expenses</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>0.024293</v>
+        <v>0.115203</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.025464</v>
+        <v>0.167383</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.10131</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.029431</v>
+        <v>0.130834</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -4241,18 +4423,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>General exploration expenses</t>
+          <t>Management and consulting fees</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>0.043128</v>
+        <v>0.512956</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>0.262</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.003491</v>
+        <v>0.249862</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4273,27 +4455,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Registration, listing fees and shareholders information</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.034867</v>
+      <c r="E32" s="5" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.034201</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.033244</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -4309,27 +4487,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Impairment of mining rights 5</t>
+          <t>Insurance and office expenses</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0.266062</v>
+      <c r="E33" s="5" t="n">
+        <v>0.024293</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.025464</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.10131</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -4345,31 +4519,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 6</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0.439515</v>
+          <t>General exploration expenses</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0.043128</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.003491</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -4398,8 +4564,10 @@
       <c r="G35" s="5" t="n">
         <v>0.511758</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>1.118511</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -4415,7 +4583,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>Finance expense / (income) 5a)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4424,16 +4592,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="5" t="n">
+        <v>0.019025</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>-0.033823</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>-0.013824</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -4498,8 +4666,10 @@
       <c r="G38" s="5" t="n">
         <v>0.154585</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>0.178058</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -4530,8 +4700,10 @@
       <c r="G39" s="5" t="n">
         <v>0.074383</v>
       </c>
-      <c r="H39" s="5" t="n">
-        <v>0.164234</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -4562,8 +4734,10 @@
       <c r="G40" s="5" t="n">
         <v>0.586141</v>
       </c>
-      <c r="H40" s="5" t="n">
-        <v>1.282745</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -4579,7 +4753,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4589,13 +4763,17 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.605307</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.586141</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>1.282745</v>
+        <v>-0.012473</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -4611,7 +4789,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (1)</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4620,16 +4798,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" s="5" t="n">
+        <v>0.605307</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>31.224204</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>31.224204</v>
+        <v>0.586141</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -4645,7 +4823,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (1)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -4654,16 +4832,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>123.825193</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.9e-08</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>4.1e-08</v>
+        <v>121.902707</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -4674,25 +4852,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Balance of purchase price receivable 5 a)</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>0.375838</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.081263</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-09</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>5e-09</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4708,20 +4886,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Convertible debentures 7</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>0.781778</v>
+          <t>Short-term investments</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.784172</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4742,24 +4926,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Total non-current liabilities</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TotalNonCurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Share subscription receivable</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.781778</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0.784172</v>
+        <v>0.125025</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4780,27 +4962,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Advances to a related company</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>1.766887</v>
+        <v>0.034867</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1.753867</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>1.587665</v>
+        <v>0.034867</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4816,25 +4996,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Equity component of the convertible debentures</t>
+          <t>Flow-through share liability 9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.562455</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.562455</v>
+      <c r="E48" s="5" t="n">
+        <v>0.012473</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4850,25 +5032,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Finance expense / (income) 5a)</t>
+          <t>Equity component of the convertible debentures 8</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>0.562455</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.019025</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.033823</v>
+        <v>0.562455</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4889,17 +5071,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Share based compensation 11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-0.012473</v>
+      <c r="E50" s="5" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4925,20 +5107,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>123.825193</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>121.902707</v>
+      <c r="E51" s="5" t="n">
+        <v>0.001075</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4954,25 +5138,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>-0.05002</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>5e-09</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>5e-09</v>
+        <v>-0.06775399999999999</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4988,26 +5172,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Short-term investments</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ShortTermInvestments</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finance expense 12</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>0.201559</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>1</v>
+        <v>0.196458</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -5028,22 +5206,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share subscription receivable</t>
+          <t>Total net finance expense</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.125025</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.151539</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.128704</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5064,20 +5240,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Advances to a related company</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.034867</v>
+        <v>1.087704</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.034867</v>
+        <v>0.61778</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5098,22 +5274,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Flow-through share liability 9</t>
+          <t>Deferred income tax recovery 13</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>0.012473</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.012473</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5134,20 +5310,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Equity component of the convertible debentures 8</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.562455</v>
+        <v>1.087704</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.562455</v>
+        <v>0.605307</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5168,22 +5344,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Share based compensation 11</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>74.41446000000001</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>123.825193</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5204,22 +5378,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.001075</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.5e-08</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>5e-09</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5235,64 +5407,66 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
-        <v>-0.05002</v>
+        <v>-1.087703</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.06775399999999999</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.605307</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.586141</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>-1.282745</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Finance expense 12</t>
+          <t>Decrement of convertible debentures 7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>0.201559</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0.196458</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.042415</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -5303,168 +5477,174 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Total net finance expense</t>
+          <t>Provision for bad debts</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.151539</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.128704</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H62" s="5" t="n">
+        <v>0.034867</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Impairment of mining rights (Note 5)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>1.087704</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.61778</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>0.266062</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 13</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>-0.012473</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>0.439515</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Effective interest costs on convertible debentures 7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>1.087704</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.605307</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19719</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.19715</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.177257</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Effective interest income on balance of purchase price receivable 5 a)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>74.41446000000001</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>123.825193</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019025</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-0.033823</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5475,35 +5655,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Operating activities before changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>1.5e-08</v>
+        <v>-0.748332</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>5e-09</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.401565</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>-0.465229</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>-0.365044</v>
       </c>
     </row>
     <row r="68">
@@ -5514,30 +5690,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>-1.087703</v>
+          <t>Change in sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.605307</v>
+        <v>-0.081897</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.586141</v>
+        <v>-0.152826</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>-1.282745</v>
+        <v>0.253323</v>
       </c>
     </row>
     <row r="69">
@@ -5553,27 +5727,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Decrement of convertible debentures 7</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.014775</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.00116</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.042415</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00039</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>-0.000257</v>
       </c>
     </row>
     <row r="70">
@@ -5589,27 +5761,25 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Provision for bad debts</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in trade accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.36272</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.079702</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.0515</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.034867</v>
+        <v>0.053847</v>
       </c>
     </row>
     <row r="71">
@@ -5625,27 +5795,25 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Impairment of mining rights (Note 5)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.279997</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.162759</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-0.101716</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.266062</v>
+        <v>0.306913</v>
       </c>
     </row>
     <row r="72">
@@ -5661,31 +5829,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-1.028329</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.564324</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.566945</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.439515</v>
+        <v>-0.05813</v>
       </c>
     </row>
     <row r="73">
@@ -5696,28 +5858,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Effective interest costs on convertible debentures 7</t>
+          <t>Repayment of convertible debentures 7</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>-0.194595</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.19719</v>
+        <v>-0.216144</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.19715</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>0.177257</v>
+        <v>-0.206559</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5728,25 +5890,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Effective interest income on balance of purchase price receivable 5 a)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.019025</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.033823</v>
+        <v>-0.206559</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5762,26 +5930,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Operating activities before changes in non-cash working capital items</t>
+          <t>Decrease in short-term investments</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>-0.748332</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-0.401565</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.465229</v>
+        <v>0.73</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>-0.365044</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="76">
@@ -5792,12 +5964,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Change in sales tax receivable</t>
+          <t>Proceeds from balance of purchase price receivable 5 a)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5806,14 +5978,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>-0.081897</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.152826</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0.253323</v>
+        <v>0.294378</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5824,30 +6000,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Change in prepaid expenses</t>
+          <t>Government grants applied against exploration and evaluation assets 6</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0.014775</v>
+        <v>0.007</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.00116</v>
+        <v>0.0216</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.00039</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>-0.000257</v>
+        <v>0.055</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5858,30 +6036,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Change in trade accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Acquisition of mining properties 5</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>-0.36272</v>
+        <v>-0.035</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.079702</v>
+        <v>-0.07728</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0515</v>
+        <v>-0.026661</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.053847</v>
+        <v>-0.039407</v>
       </c>
     </row>
     <row r="79">
@@ -5892,30 +6066,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Increase in exploration and evaluation assets 14</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>-0.279997</v>
+        <v>-0.509202</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.162759</v>
+        <v>-0.497483</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.101716</v>
+        <v>-1.570394</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.306913</v>
+        <v>-0.048408</v>
       </c>
     </row>
     <row r="80">
@@ -5926,30 +6100,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>-1.028329</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>-0.564324</v>
+          <t>Cash flows provided from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.566945</v>
+        <v>-0.5176770000000001</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>-0.05813</v>
+        <v>0.037185</v>
       </c>
     </row>
     <row r="81">
@@ -5960,28 +6134,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Repayment of convertible debentures 7</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
-        <v>-0.194595</v>
+        <v>-1.304385</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>-0.216144</v>
+        <v>0.470684</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.206559</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.291182</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-0.020946</v>
       </c>
     </row>
     <row r="82">
@@ -5992,36 +6168,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cash flows used in financing activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>2.234048</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.929663</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.206559</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.400347</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.109165</v>
       </c>
     </row>
     <row r="83">
@@ -6037,25 +6207,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Decrease in short-term investments</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.929663</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1.400347</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.73</v>
+        <v>0.109165</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.125</v>
+        <v>0.08821900000000001</v>
       </c>
     </row>
     <row r="84">
@@ -6066,12 +6236,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Proceeds from balance of purchase price receivable 5 a)</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6080,13 +6250,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>0.294378</v>
+      <c r="F84" s="5" t="n">
+        <v>-0.012473</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6102,27 +6272,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Government grants applied against exploration and evaluation assets 6</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.007</v>
+          <t>Proceeds from issuance of shares and units 9</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.055</v>
+        <v>2.51554</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6138,26 +6308,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Acquisition of mining properties 5</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>-0.035</v>
+          <t>Share issuance costs 9</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.07728</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>-0.026661</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>-0.039407</v>
+        <v>-0.029473</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -6168,30 +6348,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Increase in exploration and evaluation assets 14</t>
+          <t>Cash flows provided from financing activities</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>-0.509202</v>
+        <v>0.023214</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.497483</v>
+        <v>2.269923</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-1.570394</v>
-      </c>
-      <c r="H87" s="5" t="n">
-        <v>-0.048408</v>
+        <v>-0.206559</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -6207,7 +6389,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cash flows provided from (used in) investing activities</t>
+          <t>Decrease/(Increase) in short-term investments</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6216,16 +6398,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.5176770000000001</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>0.037185</v>
+        <v>0.73</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -6241,25 +6423,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>-1.304385</v>
+          <t>Proceeds from balance of purchase price receivable 5a)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.470684</v>
+        <v>0.318246</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-1.291182</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>-0.020946</v>
+        <v>0.294378</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -6275,25 +6457,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2.234048</v>
+        <v>-0.29927</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.929663</v>
+        <v>-1.234917</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.400347</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>0.109165</v>
+        <v>-0.5176770000000001</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -6304,30 +6488,36 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Share based compensation</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.929663</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>1.400347</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.109165</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0.08821900000000001</v>
+        <v>0.187</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -6343,17 +6533,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Effective interest costs on convertible debentures 12</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="5" t="n">
+        <v>0.202391</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.012473</v>
+        <v>0.19719</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6374,22 +6562,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares and units 9</t>
+          <t>Effective interest income on balance of purchase price receivable 5a)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>-0.05002</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>2.51554</v>
+        <v>0.019025</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6410,26 +6596,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Share issuance costs 9</t>
+          <t>Change in accounts receivable</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0.091014</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.029473</v>
+        <v>-0.081897</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6450,27 +6634,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cash flows provided from financing activities</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in advances to related company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="n">
-        <v>0.023214</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>2.269923</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.206559</v>
+        <v>-0.023066</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6486,25 +6670,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Decrease/(Increase) in short-term investments</t>
+          <t>Proceeds from issuance of shares and units 10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E96" s="5" t="n">
+        <v>0.232124</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0.73</v>
+        <v>2.51554</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6520,25 +6704,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Proceeds from balance of purchase price receivable 5a)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs 10</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>-0.014315</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.318246</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>0.294378</v>
+        <v>-0.029473</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6559,22 +6747,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>-0.29927</v>
+          <t>Increase in short-term investment</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-1.234917</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.5176770000000001</v>
+        <v>-1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6590,26 +6778,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Proceeds from balance of purchase price receivable 5a</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" s="5" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.235723</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.318246</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6630,20 +6812,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Effective interest costs on convertible debentures 12</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Tax credits applied against exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
-        <v>0.202391</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.19719</v>
+        <v>0.002209</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6651,296 +6839,6 @@
         </is>
       </c>
       <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Effective interest income on balance of purchase price receivable 5a)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>-0.05002</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0.019025</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Change in accounts receivable</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0.091014</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>-0.081897</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Change in advances to related company</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>-0.023066</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Proceeds from issuance of shares and units 10</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>0.232124</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>2.51554</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Share issuance costs 10</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>-0.014315</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>-0.029473</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Increase in short-term investment</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Proceeds from balance of purchase price receivable 5a</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>0.235723</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0.318246</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tax credits applied against exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>0.002209</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/SLA.xlsx
+++ b/output/pdf_financials_xlsx/SLA.xlsx
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.929663</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.400347</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.109165</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.929663</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1</v>
+        <v>2.400347</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.27</v>
+        <v>0.379165</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.554648</v>
+        <v>0.624985</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.858771</v>
+        <v>0.458424</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.388687</v>
+        <v>0.279522</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SLA.xlsx
+++ b/output/pdf_financials_xlsx/SLA.xlsx
@@ -1277,10 +1277,8 @@
       <c r="D34" s="3" t="n">
         <v>0.109165</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="3" t="n">
+        <v>0.08821900000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1298,10 +1296,8 @@
       <c r="D35" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="3" t="n">
+        <v>0.145</v>
       </c>
     </row>
     <row r="36">
@@ -1319,10 +1315,8 @@
       <c r="D36" s="3" t="n">
         <v>0.379165</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="3" t="n">
+        <v>0.233219</v>
       </c>
     </row>
     <row r="37">
@@ -1340,10 +1334,8 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1361,10 +1353,8 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1382,10 +1372,8 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1403,10 +1391,8 @@
       <c r="D40" s="3" t="n">
         <v>0.267928</v>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="3" t="n">
+        <v>0.014605</v>
       </c>
     </row>
     <row r="41">
@@ -1424,10 +1410,8 @@
       <c r="D41" s="3" t="n">
         <v>0.267928</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="3" t="n">
+        <v>0.014605</v>
       </c>
     </row>
     <row r="42">
@@ -1445,10 +1429,8 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1466,10 +1448,8 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1487,10 +1467,8 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1508,10 +1486,8 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1529,10 +1505,8 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1550,10 +1524,8 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1571,10 +1543,8 @@
       <c r="D48" s="3" t="n">
         <v>0.279522</v>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="3" t="n">
+        <v>0.244913</v>
       </c>
     </row>
     <row r="49">
@@ -1592,10 +1562,8 @@
       <c r="D49" s="3" t="n">
         <v>0.926615</v>
       </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="3" t="n">
+        <v>0.492737</v>
       </c>
     </row>
     <row r="50">
@@ -1613,10 +1581,8 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1634,10 +1600,8 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1655,10 +1619,8 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1676,10 +1638,8 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1697,10 +1657,8 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1745,10 +1703,8 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1766,10 +1722,8 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1787,10 +1741,8 @@
       <c r="D58" s="3" t="n">
         <v>2.991209</v>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="3" t="n">
+        <v>3.039766</v>
       </c>
     </row>
     <row r="59">
@@ -1808,10 +1760,8 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1829,10 +1779,8 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1850,10 +1798,8 @@
       <c r="D61" s="3" t="n">
         <v>8.73808</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="3" t="n">
+        <v>8.082017</v>
       </c>
     </row>
     <row r="62">
@@ -1871,10 +1817,8 @@
       <c r="D62" s="3" t="n">
         <v>11.729289</v>
       </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="3" t="n">
+        <v>11.121783</v>
       </c>
     </row>
     <row r="63">
@@ -1892,10 +1836,8 @@
       <c r="D63" s="3" t="n">
         <v>12.655904</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="3" t="n">
+        <v>11.61452</v>
       </c>
     </row>
     <row r="64">
@@ -1913,10 +1855,8 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1934,10 +1874,8 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1955,10 +1893,8 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1976,10 +1912,8 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1997,10 +1931,8 @@
       <c r="D68" s="3" t="n">
         <v>0.30831</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="3" t="n">
+        <v>0.372413</v>
       </c>
     </row>
     <row r="69">
@@ -2018,10 +1950,8 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2039,10 +1969,8 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2060,10 +1988,8 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2081,10 +2007,8 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2102,10 +2026,8 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2123,10 +2045,8 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2144,10 +2064,8 @@
       <c r="D75" s="3" t="n">
         <v>1.279355</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="3" t="n">
+        <v>1.456613</v>
       </c>
     </row>
     <row r="76">
@@ -2165,10 +2083,8 @@
       <c r="D76" s="3" t="n">
         <v>1.587665</v>
       </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="3" t="n">
+        <v>1.829026</v>
       </c>
     </row>
     <row r="77">
@@ -2186,10 +2102,8 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2207,10 +2121,8 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2228,10 +2140,8 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2276,10 +2186,8 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2297,10 +2205,8 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2318,10 +2224,8 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2339,10 +2243,8 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2360,10 +2262,8 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2381,10 +2281,8 @@
       <c r="D86" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2402,10 +2300,8 @@
       <c r="D87" s="3" t="n">
         <v>1.587665</v>
       </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="3" t="n">
+        <v>1.829026</v>
       </c>
     </row>
     <row r="88">
@@ -2423,10 +2319,8 @@
       <c r="D88" s="3" t="n">
         <v>19.239628</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="3" t="n">
+        <v>19.239628</v>
       </c>
     </row>
     <row r="89">
@@ -2444,10 +2338,8 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2465,10 +2357,8 @@
       <c r="D90" s="3" t="n">
         <v>-13.984437</v>
       </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="3" t="n">
+        <v>-15.267182</v>
       </c>
     </row>
     <row r="91">
@@ -2486,10 +2376,8 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2507,10 +2395,8 @@
       <c r="D92" s="3" t="n">
         <v>4.702907</v>
       </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="3" t="n">
+        <v>4.921767</v>
       </c>
     </row>
     <row r="93">
@@ -2528,10 +2414,8 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2549,10 +2433,8 @@
       <c r="D94" s="3" t="n">
         <v>11.068239</v>
       </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="3" t="n">
+        <v>9.785494</v>
       </c>
     </row>
     <row r="95">
@@ -2570,10 +2452,8 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2591,10 +2471,8 @@
       <c r="D96" s="3" t="n">
         <v>11.068239</v>
       </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E96" s="3" t="n">
+        <v>9.785494</v>
       </c>
     </row>
     <row r="97">
@@ -2612,10 +2490,8 @@
       <c r="D97" s="3" t="n">
         <v>0.8745514346505789</v>
       </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="3" t="n">
+        <v>0.8425224632615037</v>
       </c>
     </row>
     <row r="98">
@@ -3351,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3432,10 +3308,8 @@
       <c r="G2" s="5" t="n">
         <v>0.109165</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H2" s="5" t="n">
+        <v>0.08821900000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3470,10 +3344,8 @@
       <c r="G3" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H3" s="5" t="n">
+        <v>0.145</v>
       </c>
     </row>
     <row r="4">
@@ -3506,10 +3378,8 @@
       <c r="G4" s="5" t="n">
         <v>0.267928</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H4" s="5" t="n">
+        <v>0.014605</v>
       </c>
     </row>
     <row r="5">
@@ -3576,10 +3446,8 @@
       <c r="G6" s="5" t="n">
         <v>0.004569</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H6" s="5" t="n">
+        <v>0.004827</v>
       </c>
     </row>
     <row r="7">
@@ -3608,10 +3476,8 @@
       <c r="G7" s="5" t="n">
         <v>0.240086</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H7" s="5" t="n">
+        <v>0.240086</v>
       </c>
     </row>
     <row r="8">
@@ -3644,10 +3510,8 @@
       <c r="G8" s="5" t="n">
         <v>0.926615</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="5" t="n">
+        <v>0.492737</v>
       </c>
     </row>
     <row r="9">
@@ -3676,10 +3540,8 @@
       <c r="G9" s="5" t="n">
         <v>8.738079000000001</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H9" s="5" t="n">
+        <v>8.521532000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3712,10 +3574,8 @@
       <c r="G10" s="5" t="n">
         <v>2.991209</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H10" s="5" t="n">
+        <v>2.600251</v>
       </c>
     </row>
     <row r="11">
@@ -3731,25 +3591,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Balance of purchase price receivable 5 a)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Total non-current assets</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>0.375838</v>
+        <v>10.077679</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.081263</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.434374</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>11.729289</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.121783</v>
       </c>
     </row>
     <row r="12">
@@ -3765,27 +3625,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total non-current assets</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalNonCurrentAssets</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>10.077679</v>
+        <v>11.665532</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>10.434374</v>
+        <v>13.408247</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>11.729289</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.655904</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.61452</v>
       </c>
     </row>
     <row r="13">
@@ -3796,32 +3654,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Trade accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>11.665532</v>
+        <v>0.404279</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>13.408247</v>
+        <v>0.422686</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>12.655904</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.30831</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.372413</v>
       </c>
     </row>
     <row r="14">
@@ -3837,27 +3693,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trade accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
+          <t>Grants refundable 8</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" s="5" t="n">
-        <v>0.404279</v>
+        <v>0.33732</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.422686</v>
+        <v>0.33732</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.30831</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.33732</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.33732</v>
       </c>
     </row>
     <row r="15">
@@ -3873,23 +3723,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Grants refundable 8</t>
+          <t>Current portion of convertible debentures 7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>0.33732</v>
+        <v>0.231037</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.33732</v>
+        <v>0.209689</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.33732</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.942036</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1.119293</v>
       </c>
     </row>
     <row r="16">
@@ -3905,23 +3753,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Current portion of convertible debentures 7</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Total current liabilities</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
-        <v>0.231037</v>
+        <v>0.985109</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.209689</v>
+        <v>0.969695</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.942036</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.587665</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.829026</v>
       </c>
     </row>
     <row r="17">
@@ -3937,27 +3787,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total current liabilities</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0.985109</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.969695</v>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G17" s="5" t="n">
         <v>1.587665</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H17" s="5" t="n">
+        <v>1.829026</v>
       </c>
     </row>
     <row r="18">
@@ -3968,30 +3820,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Convertible debentures 7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Share capital 9</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>0.781778</v>
+        <v>17.640824</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.784172</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.273885</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.239628</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19.239628</v>
       </c>
     </row>
     <row r="19">
@@ -4002,34 +3854,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Total non-current liabilities</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TotalNonCurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Warrants 9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" s="5" t="n">
-        <v>0.781778</v>
+        <v>0.924554</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.784172</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5972730000000001</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.422795</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.76639</v>
       </c>
     </row>
     <row r="20">
@@ -4040,32 +3884,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Share options 10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" s="5" t="n">
-        <v>1.766887</v>
+        <v>0.435175</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1.753867</v>
+        <v>0.144092</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.587665</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.124892</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.124892</v>
       </c>
     </row>
     <row r="21">
@@ -4081,22 +3919,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share capital 9</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>17.640824</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>19.273885</v>
+          <t>Equity component of the convertible debentures 4.13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>19.239628</v>
+        <v>0.562455</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4117,23 +3955,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Warrants 9</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
-        <v>0.924554</v>
+        <v>3.128626</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.5972730000000001</v>
+        <v>4.47497</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.422795</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.702907</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4.921767</v>
       </c>
     </row>
     <row r="23">
@@ -4149,23 +3989,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share options 10</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>0.435175</v>
+        <v>-12.792989</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.144092</v>
+        <v>-13.398296</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.124892</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-13.984437</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-15.267182</v>
       </c>
     </row>
     <row r="24">
@@ -4181,25 +4023,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Equity component of the convertible debentures</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.898645</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.562455</v>
+        <v>11.65438</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.562455</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.068239</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>9.785494</v>
       </c>
     </row>
     <row r="25">
@@ -4215,27 +4057,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Total liabilities and equity</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3.128626</v>
+        <v>11.665532</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>4.47497</v>
+        <v>13.408247</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4.702907</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.655904</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>11.61452</v>
       </c>
     </row>
     <row r="26">
@@ -4251,27 +4091,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
+          <t>These consolidated financial statements were approved and authorized for issue by the Board of Directors on November</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>-12.792989</v>
+        <v>0.002023</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-13.398296</v>
+        <v>0.002024</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-13.984437</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1.8e-05</v>
       </c>
     </row>
     <row r="27">
@@ -4282,32 +4116,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>9.898645</v>
+        <v>0.115203</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>11.65438</v>
+        <v>0.167383</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>11.068239</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130834</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.071062</v>
       </c>
     </row>
     <row r="28">
@@ -4318,32 +4146,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Total liabilities and equity</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>Management and consulting fees</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>11.665532</v>
+        <v>0.512956</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>13.408247</v>
+        <v>0.262</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>12.655904</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.249862</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.250687</v>
       </c>
     </row>
     <row r="29">
@@ -4354,28 +4176,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>These consolidated financial statements were approved and authorized for issue by the Board of Directors on November</t>
+          <t>Registration, listing fees and shareholders information</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.05251</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.034201</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.5e-05</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033244</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.026887</v>
       </c>
     </row>
     <row r="30">
@@ -4391,23 +4211,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Insurance and office expenses</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>0.115203</v>
+        <v>0.024293</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.167383</v>
+        <v>0.025464</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.130834</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.10131</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.029431</v>
       </c>
     </row>
     <row r="31">
@@ -4423,18 +4241,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Management and consulting fees</t>
+          <t>General exploration expenses</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>0.512956</v>
+        <v>0.043128</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.262</v>
+        <v>2.8e-05</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.249862</v>
+        <v>-0.003491</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4455,23 +4273,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Registration, listing fees and shareholders information</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0.05251</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0.034201</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.033244</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.034867</v>
       </c>
     </row>
     <row r="33">
@@ -4487,23 +4309,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Insurance and office expenses</t>
+          <t>Impairment of mining rights 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>0.024293</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0.025464</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.10131</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.266062</v>
       </c>
     </row>
     <row r="34">
@@ -4519,23 +4345,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>General exploration expenses</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.043128</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>-0.003491</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Impairment of exploration and evaluation assets 6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.439515</v>
       </c>
     </row>
     <row r="35">
@@ -4564,10 +4398,8 @@
       <c r="G35" s="5" t="n">
         <v>0.511758</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H35" s="5" t="n">
+        <v>1.118511</v>
       </c>
     </row>
     <row r="36">
@@ -4583,7 +4415,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finance expense / (income) 5a)</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4592,16 +4424,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.019025</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" s="5" t="n">
         <v>-0.033823</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H36" s="5" t="n">
+        <v>-0.013824</v>
       </c>
     </row>
     <row r="37">
@@ -4666,10 +4498,8 @@
       <c r="G38" s="5" t="n">
         <v>0.154585</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>0.178058</v>
       </c>
     </row>
     <row r="39">
@@ -4700,10 +4530,8 @@
       <c r="G39" s="5" t="n">
         <v>0.074383</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H39" s="5" t="n">
+        <v>0.164234</v>
       </c>
     </row>
     <row r="40">
@@ -4734,10 +4562,8 @@
       <c r="G40" s="5" t="n">
         <v>0.586141</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>1.282745</v>
       </c>
     </row>
     <row r="41">
@@ -4753,7 +4579,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4763,17 +4589,13 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.012473</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.605307</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.586141</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.282745</v>
       </c>
     </row>
     <row r="42">
@@ -4789,7 +4611,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Weighted average number of common shares outstanding (1)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4798,16 +4620,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.605307</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.586141</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.224204</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>31.224204</v>
       </c>
     </row>
     <row r="43">
@@ -4823,7 +4645,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Basic and diluted loss per share (1)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -4832,16 +4654,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>123.825193</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>121.902707</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.9e-08</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>4.1e-08</v>
       </c>
     </row>
     <row r="44">
@@ -4852,25 +4674,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Balance of purchase price receivable 5 a)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>0.375838</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>5e-09</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>5e-09</v>
+        <v>0.081263</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4886,26 +4708,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Short-term investments</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ShortTermInvestments</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Convertible debentures 7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>0.781778</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>1</v>
+        <v>0.784172</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4926,22 +4742,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Share subscription receivable</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Total non-current liabilities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>0.125025</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.781778</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.784172</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4962,25 +4780,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Advances to a related company</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>0.034867</v>
+        <v>1.766887</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.034867</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.753867</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.587665</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4996,27 +4816,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Flow-through share liability 9</t>
+          <t>Equity component of the convertible debentures</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>0.012473</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.562455</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.562455</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5032,25 +4850,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Equity component of the convertible debentures 8</t>
+          <t>Finance expense / (income) 5a)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>0.562455</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.562455</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019025</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.033823</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5071,17 +4889,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share based compensation 11</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.012473</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5107,22 +4925,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>0.001075</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>123.825193</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>121.902707</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5138,25 +4954,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>-0.05002</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.06775399999999999</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-09</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>5e-09</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5172,20 +4988,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Finance expense 12</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.201559</v>
+          <t>Short-term investments</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.196458</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -5206,20 +5028,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Total net finance expense</t>
+          <t>Share subscription receivable</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.151539</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.128704</v>
+        <v>0.125025</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5240,20 +5064,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Advances to a related company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>1.087704</v>
+        <v>0.034867</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.61778</v>
+        <v>0.034867</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5274,22 +5098,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 13</t>
+          <t>Flow-through share liability 9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>-0.012473</v>
+      <c r="E56" s="5" t="n">
+        <v>0.012473</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5310,20 +5134,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Equity component of the convertible debentures 8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>1.087704</v>
+        <v>0.562455</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.605307</v>
+        <v>0.562455</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5344,20 +5168,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Share based compensation 11</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>74.41446000000001</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>123.825193</v>
+        <v>0.187</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5378,20 +5204,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>1.5e-08</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>5e-09</v>
+        <v>0.001075</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5407,66 +5235,64 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>-1.087703</v>
+        <v>-0.05002</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.605307</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.586141</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>-1.282745</v>
+        <v>-0.06775399999999999</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Decrement of convertible debentures 7</t>
+          <t>Finance expense 12</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.042415</v>
+      <c r="E61" s="5" t="n">
+        <v>0.201559</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.196458</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -5477,174 +5303,168 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Provision for bad debts</t>
+          <t>Total net finance expense</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="5" t="n">
+        <v>0.151539</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.128704</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n">
-        <v>0.034867</v>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Impairment of mining rights (Note 5)</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="5" t="n">
+        <v>1.087704</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.61778</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n">
-        <v>0.266062</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 6)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Deferred income tax recovery 13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>-0.012473</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
-        <v>0.439515</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Effective interest costs on convertible debentures 7</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="5" t="n">
+        <v>1.087704</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.19719</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.19715</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>0.177257</v>
+        <v>0.605307</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Effective interest income on balance of purchase price receivable 5 a)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>74.41446000000001</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.019025</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.033823</v>
+        <v>123.825193</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5655,31 +5475,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Operating activities before changes in non-cash working capital items</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>-0.748332</v>
+        <v>1.5e-08</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.401565</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-0.465229</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>-0.365044</v>
+        <v>5e-09</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -5690,28 +5514,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Change in sales tax receivable</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>-1.087703</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.081897</v>
+        <v>-0.605307</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.152826</v>
+        <v>-0.586141</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.253323</v>
+        <v>-1.282745</v>
       </c>
     </row>
     <row r="69">
@@ -5727,25 +5553,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Change in prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0.014775</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>-0.00116</v>
+          <t>Decrement of convertible debentures 7</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.00039</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>-0.000257</v>
+        <v>-0.042415</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5761,25 +5589,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Change in trade accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>-0.36272</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>-0.079702</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>0.0515</v>
+          <t>Provision for bad debts</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.053847</v>
+        <v>0.034867</v>
       </c>
     </row>
     <row r="71">
@@ -5795,25 +5625,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>-0.279997</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.162759</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>-0.101716</v>
+          <t>Impairment of mining rights (Note 5)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.306913</v>
+        <v>0.266062</v>
       </c>
     </row>
     <row r="72">
@@ -5829,25 +5661,31 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
+          <t>Impairment of exploration and evaluation assets (Note 6)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>-1.028329</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.564324</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>-0.566945</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.05813</v>
+        <v>0.439515</v>
       </c>
     </row>
     <row r="73">
@@ -5858,28 +5696,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Repayment of convertible debentures 7</t>
+          <t>Effective interest costs on convertible debentures 7</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>-0.194595</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.216144</v>
+        <v>0.19719</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.206559</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19715</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.177257</v>
       </c>
     </row>
     <row r="74">
@@ -5890,31 +5728,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash flows used in financing activities</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Effective interest income on balance of purchase price receivable 5 a)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>0.019025</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.206559</v>
+        <v>-0.033823</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5930,30 +5762,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Decrease in short-term investments</t>
+          <t>Operating activities before changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>-0.748332</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-0.401565</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.73</v>
+        <v>-0.465229</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.125</v>
+        <v>-0.365044</v>
       </c>
     </row>
     <row r="76">
@@ -5964,12 +5792,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Proceeds from balance of purchase price receivable 5 a)</t>
+          <t>Change in sales tax receivable</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5978,18 +5806,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>-0.081897</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.294378</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.152826</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.253323</v>
       </c>
     </row>
     <row r="77">
@@ -6000,32 +5824,30 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Government grants applied against exploration and evaluation assets 6</t>
+          <t>Change in prepaid expenses</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0.007</v>
+        <v>0.014775</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.0216</v>
+        <v>-0.00116</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00039</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-0.000257</v>
       </c>
     </row>
     <row r="78">
@@ -6036,26 +5858,30 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Acquisition of mining properties 5</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Change in trade accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.36272</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.07728</v>
+        <v>-0.079702</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.026661</v>
+        <v>0.0515</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>-0.039407</v>
+        <v>0.053847</v>
       </c>
     </row>
     <row r="79">
@@ -6066,30 +5892,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Increase in exploration and evaluation assets 14</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>-0.509202</v>
+        <v>-0.279997</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.497483</v>
+        <v>-0.162759</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-1.570394</v>
+        <v>-0.101716</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>-0.048408</v>
+        <v>0.306913</v>
       </c>
     </row>
     <row r="80">
@@ -6100,30 +5926,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cash flows provided from (used in) investing activities</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-1.028329</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-0.564324</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.5176770000000001</v>
+        <v>-0.566945</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.037185</v>
+        <v>-0.05813</v>
       </c>
     </row>
     <row r="81">
@@ -6134,30 +5960,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Repayment of convertible debentures 7</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>-1.304385</v>
+        <v>-0.194595</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.470684</v>
+        <v>-0.216144</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-1.291182</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>-0.020946</v>
+        <v>-0.206559</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6168,30 +5992,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash flows used in financing activities</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>2.234048</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.929663</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1.400347</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>0.109165</v>
+        <v>-0.206559</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -6207,25 +6037,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.929663</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>1.400347</v>
+          <t>Decrease in short-term investments</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.109165</v>
+        <v>0.73</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.08821900000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="84">
@@ -6236,12 +6066,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Proceeds from balance of purchase price receivable 5 a)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6250,13 +6080,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.012473</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.294378</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6272,27 +6102,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares and units 9</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Government grants applied against exploration and evaluation assets 6</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.007</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>2.51554</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0216</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.055</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6308,36 +6138,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Share issuance costs 9</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Acquisition of mining properties 5</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>-0.035</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.029473</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07728</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-0.026661</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>-0.039407</v>
       </c>
     </row>
     <row r="87">
@@ -6348,32 +6168,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cash flows provided from financing activities</t>
+          <t>Increase in exploration and evaluation assets 14</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.023214</v>
+        <v>-0.509202</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>2.269923</v>
+        <v>-0.497483</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.206559</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.570394</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-0.048408</v>
       </c>
     </row>
     <row r="88">
@@ -6389,7 +6207,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Decrease/(Increase) in short-term investments</t>
+          <t>Cash flows provided from (used in) investing activities</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6398,16 +6216,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>-1</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.5176770000000001</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.037185</v>
       </c>
     </row>
     <row r="89">
@@ -6423,25 +6241,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Proceeds from balance of purchase price receivable 5a)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>-1.304385</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.318246</v>
+        <v>0.470684</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.294378</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.291182</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-0.020946</v>
       </c>
     </row>
     <row r="90">
@@ -6457,27 +6275,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.29927</v>
+        <v>2.234048</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-1.234917</v>
+        <v>0.929663</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.5176770000000001</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.400347</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.109165</v>
       </c>
     </row>
     <row r="91">
@@ -6488,36 +6304,30 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.929663</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>1.400347</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.109165</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.08821900000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6533,15 +6343,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Effective interest costs on convertible debentures 12</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>0.202391</v>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.19719</v>
+        <v>-0.012473</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6562,20 +6378,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Effective interest income on balance of purchase price receivable 5a)</t>
+          <t>Proceeds from issuance of shares and units 9</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>-0.05002</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.019025</v>
+        <v>2.51554</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6596,24 +6414,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Change in accounts receivable</t>
+          <t>Share issuance costs 9</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0.091014</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.081897</v>
+        <v>-0.029473</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6634,27 +6454,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Change in advances to related company</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Cash flows provided from financing activities</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
-        <v>-0.023066</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023214</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>2.269923</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.206559</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6670,25 +6490,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares and units 10</t>
+          <t>Decrease/(Increase) in short-term investments</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>0.232124</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>2.51554</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.73</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6704,29 +6524,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Share issuance costs 10</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>-0.014315</v>
+          <t>Proceeds from balance of purchase price receivable 5a)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>-0.029473</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.318246</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.294378</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6747,22 +6563,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Increase in short-term investment</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-0.29927</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.234917</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.5176770000000001</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6778,20 +6594,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Proceeds from balance of purchase price receivable 5a</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
-        <v>0.235723</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>0.318246</v>
+        <v>0.187</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6812,33 +6634,317 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Effective interest costs on convertible debentures 12</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>0.202391</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Effective interest income on balance of purchase price receivable 5a)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>-0.05002</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.019025</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Change in accounts receivable</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.091014</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-0.081897</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Change in advances to related company</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>-0.023066</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of shares and units 10</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>0.232124</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>2.51554</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Share issuance costs 10</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>-0.014315</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>-0.029473</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>Investing activities</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Increase in short-term investment</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Proceeds from balance of purchase price receivable 5a</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.235723</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.318246</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
         <is>
           <t>Tax credits applied against exploration and evaluation assets</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>NetOtherInvestingChanges</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E108" s="5" t="n">
         <v>0.002209</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
